--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486884_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486884_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. GATELL SANZ</t>
+          <t>J. JIMÉNEZ JIMÉNEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.745</v>
+        <v>2.7201</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3873</v>
+        <v>1.4447</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3577</v>
+        <v>1.2754</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9293</v>
+        <v>1.5384</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8978</v>
+        <v>0.3046</v>
       </c>
       <c r="I2" t="n">
-        <v>2.0315</v>
+        <v>1.2338</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7861</v>
+        <v>1.7424</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9179</v>
+        <v>0.7431</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8682</v>
+        <v>0.9993</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1432</v>
+        <v>-0.204</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0201</v>
+        <v>-0.4385</v>
       </c>
       <c r="O2" t="n">
-        <v>1.1633</v>
+        <v>0.2345</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>1.0267</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0534</v>
+        <v>-1.2321</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0534</v>
+        <v>2.2588</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0057</v>
+        <v>0.155</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4144</v>
+        <v>-0.2443</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.42</v>
+        <v>0.3993</v>
       </c>
       <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.1786</v>
+      </c>
+      <c r="X2" t="n">
         <v>-1.1786</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.2402</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-1.4189</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ JIMÉNEZ</t>
+          <t>D. ARJOL LOPEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7209</v>
+        <v>2.3111</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2084</v>
+        <v>0.8821</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5125</v>
+        <v>1.4291</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5384</v>
+        <v>1.0647</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3046</v>
+        <v>2.0989</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2338</v>
+        <v>-1.0342</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7424</v>
+        <v>1.048</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7431</v>
+        <v>1.7588</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9993</v>
+        <v>-0.7108</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.204</v>
+        <v>0.0167</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4385</v>
+        <v>0.3401</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2345</v>
+        <v>-0.3234</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0267</v>
+        <v>0.616</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.2321</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2588</v>
+        <v>1.8481</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1558</v>
+        <v>-0.0678</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4806</v>
+        <v>-0.1125</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6364</v>
+        <v>0.0447</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
       <c r="W3" t="n">
         <v>1.1786</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1786</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6629</v>
+        <v>2.0715</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2239</v>
+        <v>0.6622</v>
       </c>
       <c r="F4" t="n">
-        <v>1.439</v>
+        <v>1.4094</v>
       </c>
       <c r="G4" t="n">
         <v>0.6138</v>
@@ -766,13 +766,13 @@
         <v>0.8214</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2277</v>
+        <v>0.6364</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1971</v>
+        <v>0.6353</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0307</v>
+        <v>0.001</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. ARJOL LOPEZ</t>
+          <t>E. GATELL SANZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8969</v>
+        <v>1.9091</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.996</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2512</v>
+        <v>0.9131</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0647</v>
+        <v>3.9293</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0989</v>
+        <v>1.8978</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0342</v>
+        <v>2.0315</v>
       </c>
       <c r="J5" t="n">
-        <v>1.048</v>
+        <v>2.7861</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7588</v>
+        <v>1.9179</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7108</v>
+        <v>0.8682</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0167</v>
+        <v>1.1432</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3401</v>
+        <v>-0.0201</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3234</v>
+        <v>1.1633</v>
       </c>
       <c r="P5" t="n">
-        <v>0.616</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.2321</v>
+        <v>-2.0534</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8481</v>
+        <v>2.0534</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.482</v>
+        <v>-0.8416</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3489</v>
+        <v>0.0231</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1331</v>
+        <v>-0.8647</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6982</v>
+        <v>-1.1786</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1786</v>
+        <v>0.2402</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4805</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4786</v>
+        <v>1.6843</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.2303</v>
+        <v>-1.2617</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7089</v>
+        <v>2.946</v>
       </c>
       <c r="G6" t="n">
         <v>1.6851</v>
@@ -922,13 +922,13 @@
         <v>2.8748</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.9108</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1121</v>
+        <v>-0.1435</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7987</v>
+        <v>-0.5615</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9384</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2062</v>
+        <v>-0.0574</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4216</v>
+        <v>-0.7742</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6279</v>
+        <v>0.7168</v>
       </c>
       <c r="G7" t="n">
         <v>0.6816</v>
@@ -1000,13 +1000,13 @@
         <v>0.2053</v>
       </c>
       <c r="S7" t="n">
-        <v>0.346</v>
+        <v>0.0823</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5656</v>
+        <v>0.2131</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2197</v>
+        <v>-0.1307</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4722</v>
+        <v>-0.9583</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.581</v>
+        <v>-2.0968</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1088</v>
+        <v>1.1385</v>
       </c>
       <c r="G8" t="n">
         <v>1.0689</v>
@@ -1078,13 +1078,13 @@
         <v>1.6427</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.9251</v>
+        <v>-1.4112</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6587</v>
+        <v>-0.1744</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2664</v>
+        <v>-1.2367</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4731</v>
+        <v>-2.5069</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3707</v>
+        <v>-0.5528</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1023</v>
+        <v>-1.9541</v>
       </c>
       <c r="G9" t="n">
         <v>0.1023</v>
@@ -1156,13 +1156,13 @@
         <v>0.616</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.986</v>
+        <v>-1.0199</v>
       </c>
       <c r="T9" t="n">
-        <v>0.244</v>
+        <v>0.0619</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.23</v>
+        <v>-1.0818</v>
       </c>
       <c r="V9" t="n">
         <v>-1.1786</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7355</v>
+        <v>-3.3575</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.103</v>
+        <v>-2.9325</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6325</v>
+        <v>-0.425</v>
       </c>
       <c r="G10" t="n">
         <v>0.3849</v>
@@ -1234,13 +1234,13 @@
         <v>1.6427</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2991</v>
+        <v>-0.9211</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2907</v>
+        <v>-0.1203</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0083</v>
+        <v>-0.8008</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1786</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5967</v>
+        <v>-4.3125</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1414</v>
+        <v>-2.8276</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4552</v>
+        <v>-1.4849</v>
       </c>
       <c r="G11" t="n">
         <v>0.3405</v>
@@ -1312,13 +1312,13 @@
         <v>1.2321</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6702</v>
+        <v>-1.3861</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7905</v>
+        <v>-0.4767</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8798</v>
+        <v>-0.9094</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4189</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8849</v>
+        <v>-4.9673</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.7027</v>
+        <v>-4.6368</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1822</v>
+        <v>-0.3304</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2522</v>
@@ -1390,13 +1390,13 @@
         <v>1.2321</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3119</v>
+        <v>0.2295</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0386</v>
+        <v>0.1045</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2732</v>
+        <v>0.125</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0698</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.4519</v>
+        <v>-5.463799999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-12.0854</v>
+        <v>-11.0974</v>
       </c>
       <c r="F13" t="n">
-        <v>5.633799999999999</v>
+        <v>5.6339</v>
       </c>
       <c r="G13" t="n">
         <v>10.1573</v>
@@ -1441,7 +1441,7 @@
         <v>12.6558</v>
       </c>
       <c r="J13" t="n">
-        <v>6.832699999999999</v>
+        <v>6.8327</v>
       </c>
       <c r="K13" t="n">
         <v>0.9281999999999995</v>
@@ -1468,13 +1468,13 @@
         <v>16.4274</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.237500000000001</v>
+        <v>-5.2496</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2218</v>
+        <v>-0.2338000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.015700000000001</v>
+        <v>-5.0156</v>
       </c>
       <c r="V13" t="n">
         <v>-6.264699999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.605</v>
+        <v>5.1908</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2213</v>
+        <v>2.4305</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3837</v>
+        <v>2.7603</v>
       </c>
       <c r="G14" t="n">
         <v>-3.5406</v>
@@ -1546,13 +1546,13 @@
         <v>3.4908</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8786</v>
+        <v>1.4644</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5111</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3675</v>
+        <v>0.7441</v>
       </c>
       <c r="V14" t="n">
         <v>3.7761</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. MEDINA ROA</t>
+          <t>R. GARCIA SALAME</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5607</v>
+        <v>4.3548</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8718</v>
+        <v>2.2461</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6889</v>
+        <v>2.1088</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1611</v>
+        <v>0.1638</v>
       </c>
       <c r="H15" t="n">
-        <v>0.837</v>
+        <v>0.4347</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.2709</v>
       </c>
       <c r="J15" t="n">
-        <v>1.628</v>
+        <v>0.744</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4702</v>
+        <v>0.2049</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1579</v>
+        <v>0.5391</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4669</v>
+        <v>-0.5803</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6332</v>
+        <v>0.2298</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8338</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P15" t="n">
         <v>-1.0267</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.1068</v>
+        <v>-3.0801</v>
       </c>
       <c r="R15" t="n">
-        <v>3.0801</v>
+        <v>2.0534</v>
       </c>
       <c r="S15" t="n">
-        <v>4.7056</v>
+        <v>1.0926</v>
       </c>
       <c r="T15" t="n">
-        <v>3.6299</v>
+        <v>0.2167</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0757</v>
+        <v>0.8758</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7207</v>
+        <v>4.1252</v>
       </c>
       <c r="W15" t="n">
-        <v>0.7207</v>
+        <v>4.3654</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.6764</v>
+        <v>3.3555</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5015</v>
+        <v>1.3969</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1749</v>
+        <v>1.9586</v>
       </c>
       <c r="G16" t="n">
         <v>2.4683</v>
@@ -1702,13 +1702,13 @@
         <v>2.2588</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2429</v>
+        <v>0.9221</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2826</v>
+        <v>0.178</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9603</v>
+        <v>0.7441</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2402</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. GARCIA SALAME</t>
+          <t>E. MEDINA ROA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.6157</v>
+        <v>2.3501</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4093</v>
+        <v>-0.2203</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2064</v>
+        <v>2.5704</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1638</v>
+        <v>0.1611</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4347</v>
+        <v>0.837</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2709</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0.744</v>
+        <v>1.628</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2049</v>
+        <v>1.4702</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5391</v>
+        <v>0.1579</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5803</v>
+        <v>-1.4669</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2298</v>
+        <v>-0.6332</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.8338</v>
       </c>
       <c r="P17" t="n">
         <v>-1.0267</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.0801</v>
+        <v>-4.1068</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0534</v>
+        <v>3.0801</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3534</v>
+        <v>2.495</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6201</v>
+        <v>1.5378</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9735</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>4.1252</v>
+        <v>0.7207</v>
       </c>
       <c r="W17" t="n">
-        <v>4.3654</v>
+        <v>0.7207</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.926</v>
+        <v>0.6278</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2314</v>
+        <v>-2.4406</v>
       </c>
       <c r="F18" t="n">
-        <v>3.1574</v>
+        <v>3.0684</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5412</v>
@@ -1858,13 +1858,13 @@
         <v>3.0801</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4672</v>
+        <v>1.169</v>
       </c>
       <c r="T18" t="n">
-        <v>1.2434</v>
+        <v>1.0342</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2237</v>
+        <v>0.1348</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5526</v>
+        <v>0.4079</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5346</v>
+        <v>1.2208</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.982</v>
+        <v>-0.8129</v>
       </c>
       <c r="G19" t="n">
         <v>1.2272</v>
@@ -1936,13 +1936,13 @@
         <v>0.616</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.112</v>
+        <v>-0.2567</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6392</v>
+        <v>0.3254</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7512</v>
+        <v>-0.5821</v>
       </c>
       <c r="V19" t="n">
         <v>-1.1786</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.1557</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1587</v>
+        <v>-0.0541</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1505</v>
+        <v>0.2098</v>
       </c>
       <c r="G20" t="n">
         <v>0.09180000000000001</v>
@@ -2014,13 +2014,13 @@
         <v>0.616</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.716</v>
+        <v>-0.5521</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1976</v>
+        <v>-0.093</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5184</v>
+        <v>-0.4591</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1767</v>
+        <v>-0.9082</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7433</v>
+        <v>-1.5341</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5665</v>
+        <v>0.6258</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6661</v>
@@ -2092,13 +2092,13 @@
         <v>1.0267</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5106000000000001</v>
+        <v>-0.2421</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0581</v>
+        <v>0.1511</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4525</v>
+        <v>-0.3932</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2165</v>
+        <v>-2.5557</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7235</v>
+        <v>-1.4097</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4931</v>
+        <v>-1.1461</v>
       </c>
       <c r="G22" t="n">
         <v>-3.8693</v>
@@ -2170,13 +2170,13 @@
         <v>1.8481</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2569</v>
+        <v>0.4039</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0931</v>
+        <v>0.2207</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1638</v>
+        <v>0.1832</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9384</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.0832</v>
+        <v>-5.8296</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.315300000000001</v>
+        <v>-7.2693</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2322</v>
+        <v>1.4396</v>
       </c>
       <c r="G23" t="n">
         <v>-5.6524</v>
@@ -2248,13 +2248,13 @@
         <v>2.4641</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8148</v>
+        <v>0.4387</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3216</v>
+        <v>0.7244</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4931</v>
+        <v>-0.2857</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.4518</v>
+        <v>7.149100000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.633700000000001</v>
+        <v>-5.633799999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>12.0854</v>
+        <v>12.7827</v>
       </c>
       <c r="G24" t="n">
         <v>-10.1574</v>
@@ -2326,13 +2326,13 @@
         <v>20.5341</v>
       </c>
       <c r="S24" t="n">
-        <v>6.237399999999999</v>
+        <v>6.9348</v>
       </c>
       <c r="T24" t="n">
-        <v>5.015700000000001</v>
+        <v>5.0156</v>
       </c>
       <c r="U24" t="n">
-        <v>1.2217</v>
+        <v>1.9191</v>
       </c>
       <c r="V24" t="n">
         <v>6.2648</v>
